--- a/output/supplementary/P6_post_market.xlsx
+++ b/output/supplementary/P6_post_market.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,16 +588,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9626517273576097</v>
+        <v>0.9627213420316869</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001867413632119515</v>
+        <v>0.001863932898415657</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01587301587301587</v>
+        <v>0.01584342963653309</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0196078431372549</v>
+        <v>0.0195712954333644</v>
       </c>
     </row>
     <row r="3">
@@ -607,22 +607,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.625</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1428571428571428</v>
+        <v>0.125</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>NR</t>
+          <t>PMA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -635,25 +635,6 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>PMA</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="n">
         <v>0</v>
       </c>
     </row>
